--- a/artfynd/A 8113-2026 artfynd.xlsx
+++ b/artfynd/A 8113-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1545,6 +1545,125 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>133064587</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58328</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Jutakullen, nordost, Vg</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>344506</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6433330</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Lars Gerre, Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8113-2026 artfynd.xlsx
+++ b/artfynd/A 8113-2026 artfynd.xlsx
@@ -1550,7 +1550,7 @@
         <v>133064587</v>
       </c>
       <c r="B10" t="n">
-        <v>58328</v>
+        <v>58331</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 8113-2026 artfynd.xlsx
+++ b/artfynd/A 8113-2026 artfynd.xlsx
@@ -1550,7 +1550,7 @@
         <v>133064587</v>
       </c>
       <c r="B10" t="n">
-        <v>58331</v>
+        <v>58332</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 8113-2026 artfynd.xlsx
+++ b/artfynd/A 8113-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130331828</v>
+        <v>130827873</v>
       </c>
       <c r="B2" t="n">
-        <v>75327</v>
+        <v>83292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,40 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6426</v>
+        <v>306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Slerebosjön, 200 m Ö om, Vg</t>
+          <t>Jutakullen, nordost, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>344522</v>
+        <v>344451</v>
       </c>
       <c r="R2" t="n">
-        <v>6433359</v>
+        <v>6433334</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -779,50 +775,49 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna Pielach</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna Pielach</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130331824</v>
+        <v>130331874</v>
       </c>
       <c r="B3" t="n">
-        <v>97595</v>
+        <v>83299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2569</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -830,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>344482</v>
+        <v>344531</v>
       </c>
       <c r="R3" t="n">
-        <v>6433360</v>
+        <v>6433318</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -893,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130331837</v>
+        <v>130331824</v>
       </c>
       <c r="B4" t="n">
-        <v>75327</v>
+        <v>97733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,26 +899,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6426</v>
+        <v>2569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -931,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>344534</v>
+        <v>344482</v>
       </c>
       <c r="R4" t="n">
-        <v>6433351</v>
+        <v>6433360</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -994,51 +990,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130331874</v>
+        <v>130827867</v>
       </c>
       <c r="B5" t="n">
-        <v>83193</v>
+        <v>97733</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>308</v>
+        <v>2569</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Slerebosjön, 200 m Ö om, Vg</t>
+          <t>Jutakullen, nordost, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>344531</v>
+        <v>344478</v>
       </c>
       <c r="R5" t="n">
-        <v>6433318</v>
+        <v>6433317</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1076,33 +1069,32 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anna Pielach</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna Pielach</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130331854</v>
+        <v>130331828</v>
       </c>
       <c r="B6" t="n">
-        <v>75327</v>
+        <v>75428</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1133,10 +1125,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>344499</v>
+        <v>344522</v>
       </c>
       <c r="R6" t="n">
-        <v>6433329</v>
+        <v>6433359</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1211,14 +1203,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130827874</v>
+        <v>130331837</v>
       </c>
       <c r="B7" t="n">
-        <v>75350</v>
+        <v>75428</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1240,19 +1232,22 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Jutakullen, nordost, Vg</t>
+          <t>Slerebosjön, 200 m Ö om, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>344473</v>
+        <v>344534</v>
       </c>
       <c r="R7" t="n">
-        <v>6433342</v>
+        <v>6433351</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1290,81 +1285,70 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anna Pielach</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anna Pielach</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130827870</v>
+        <v>130331854</v>
       </c>
       <c r="B8" t="n">
-        <v>5197</v>
+        <v>75428</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105930</v>
+        <v>6426</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Jutakullen, nordost, Vg</t>
+          <t>Slerebosjön, 200 m Ö om, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>344458</v>
+        <v>344499</v>
       </c>
       <c r="R8" t="n">
-        <v>6433350</v>
+        <v>6433329</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1402,6 +1386,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1423,60 +1408,63 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anna Pielach</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anna Pielach</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130827873</v>
+        <v>130536318</v>
       </c>
       <c r="B9" t="n">
-        <v>83209</v>
+        <v>75428</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>306</v>
+        <v>6426</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Jutakullen, nordost, Vg</t>
+          <t>Slerebosjön, öster om, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>344451</v>
+        <v>344450</v>
       </c>
       <c r="R9" t="n">
-        <v>6433334</v>
+        <v>6433315</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1500,12 +1488,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-27</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Vid basen av en medelgrov gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1514,90 +1507,64 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Thomas Grönlund</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133064587</v>
+        <v>130827874</v>
       </c>
       <c r="B10" t="n">
-        <v>58332</v>
+        <v>75428</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>6426</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Jutakullen, nordost, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>344506</v>
+        <v>344473</v>
       </c>
       <c r="R10" t="n">
-        <v>6433330</v>
+        <v>6433342</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1624,22 +1591,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1650,19 +1607,1152 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130827875</v>
+      </c>
+      <c r="B11" t="n">
+        <v>75428</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Jutakullen, nordost, Vg</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>344478</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6433317</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130827876</v>
+      </c>
+      <c r="B12" t="n">
+        <v>75428</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Jutakullen, nordost, Vg</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>344449</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6433318</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130918028</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Drängedalen, Vg</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>344470</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6433314</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130536439</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Slerebosjön, öster om, Vg</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>344488</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6433317</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-12-27</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-12-27</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Två skitar i kanten på en sten.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130827872</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Jutakullen, nordost, Vg</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>344461</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6433331</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>133064587</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58349</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Jutakullen, nordost, Vg</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>344506</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6433330</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
           <t>Lars Gerre</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AX16" t="inlineStr">
         <is>
           <t>Lars Gerre, Thomas Grönlund</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130536468</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Slerebosjön, öster om, Vg</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>344488</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6433317</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-12-27</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-12-27</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130917555</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Drängedalen, Vg</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>344470</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6433314</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Sågs på nära håll.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130827870</v>
+      </c>
+      <c r="B19" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Jutakullen, nordost, Vg</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>344458</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6433350</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>130536410</v>
+      </c>
+      <c r="B20" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Slerebosjön, öster om, Vg</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>344514</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6433320</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-12-27</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-12-27</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Gnaghål på en björkhögstubbe.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8113-2026 artfynd.xlsx
+++ b/artfynd/A 8113-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130827873</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130331874</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130331824</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,6 +1104,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130827867</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1200,6 +1225,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130331828</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1301,6 +1331,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130331837</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1417,6 +1452,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130331854</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1523,6 +1563,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130536318</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130827874</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1747,6 +1797,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130827875</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1859,6 +1914,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130827876</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1970,6 +2030,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130918028</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2080,6 +2145,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130536439</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2177,6 +2247,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130827872</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2296,6 +2371,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133064587</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2405,6 +2485,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130536468</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2529,6 +2614,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130917555</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2641,6 +2731,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130827870</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2753,8 +2848,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130536410</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>